--- a/output/pdf_financials_xlsx/OCG.xlsx
+++ b/output/pdf_financials_xlsx/OCG.xlsx
@@ -1021,7 +1021,7 @@
         <v>-2.217208</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.782269</v>
+        <v>-2.782269</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-5.025226</v>
@@ -1225,7 +1225,7 @@
         <v>-2.217208</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.782269</v>
+        <v>-2.782269</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-5.025226</v>
@@ -1345,7 +1345,7 @@
         <v>-2.217208</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.782269</v>
+        <v>-2.782269</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-5.025226</v>
@@ -1465,7 +1465,7 @@
         <v>11.669516</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-21.402069</v>
+        <v>21.402069</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>62.815325</v>
@@ -1505,7 +1505,7 @@
         <v>-2.217208</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.782269</v>
+        <v>-2.782269</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-5.025226</v>
@@ -1585,7 +1585,7 @@
         <v>-2.202618</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.794395</v>
+        <v>-2.770143</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-4.9982</v>
@@ -1687,7 +1687,7 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -4313,34 +4313,34 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.155664</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.155664</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.696054</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.343112</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>9.292227</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>11.317286</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>13.75093</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>27.562457</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>30.708094</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>33.42719</v>
       </c>
     </row>
     <row r="93">
@@ -7319,7 +7319,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -9490,7 +9494,11 @@
           <t>Warrant reserves 12</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -10472,7 +10480,11 @@
           <t>Warrant reserves 13</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -10967,7 +10979,11 @@
           <t>Warrant reserves 12</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -12038,7 +12054,11 @@
           <t>Warrant reserves</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -31111,7 +31131,7 @@
         <v>-2.217208</v>
       </c>
       <c r="I360" s="5" t="n">
-        <v>2.782269</v>
+        <v>-2.782269</v>
       </c>
       <c r="J360" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OCG.xlsx
+++ b/output/pdf_financials_xlsx/OCG.xlsx
@@ -849,37 +849,37 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.027063</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002231</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001453</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000222</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.005712</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.01746</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.005691</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.002327</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001993</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.116485</v>
       </c>
     </row>
     <row r="13">
@@ -1493,37 +1493,37 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.878973</v>
+        <v>-1.906036</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.435358</v>
+        <v>-1.437589</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.619291</v>
+        <v>-2.620744</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.217208</v>
+        <v>-2.21743</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.782269</v>
+        <v>-2.782497</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.025226</v>
+        <v>-5.030938</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-12.846505</v>
+        <v>-12.863965</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-11.407745</v>
+        <v>-11.413436</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-9.438388</v>
+        <v>-9.440715000000001</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-10.308766</v>
+        <v>-10.310759</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-17.729217</v>
+        <v>-17.845702</v>
       </c>
     </row>
     <row r="28">
@@ -1573,37 +1573,37 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.829087</v>
+        <v>-1.85615</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.407356</v>
+        <v>-1.409587</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.599509</v>
+        <v>-2.600962</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.202618</v>
+        <v>-2.20284</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.770143</v>
+        <v>-2.770371</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.9982</v>
+        <v>-5.003912</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-12.818237</v>
+        <v>-12.835697</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-11.380649</v>
+        <v>-11.38634</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-9.379778</v>
+        <v>-9.382104999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-10.235216</v>
+        <v>-10.237209</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-17.70183</v>
+        <v>-17.818315</v>
       </c>
     </row>
     <row r="30">
@@ -1789,16 +1789,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.048</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.243911</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.200414</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.185222</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>5.952245</v>
@@ -1813,10 +1813,10 @@
         <v>3.230315</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.122749</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>5.107316</v>
       </c>
     </row>
     <row r="35">
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.04</v>
+        <v>4.088</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.22004</v>
+        <v>1.463951</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.010505</v>
+        <v>0.210919</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.00573</v>
+        <v>0.190952</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>5.957975</v>
@@ -1897,10 +1897,10 @@
         <v>3.230315</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.122749</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>2.384895</v>
+        <v>7.492211</v>
       </c>
     </row>
     <row r="37">
@@ -2377,16 +2377,16 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.200224</v>
+        <v>0.152224</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.286011</v>
+        <v>0.0421</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.387683</v>
+        <v>0.187269</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.291049</v>
+        <v>0.105827</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.329668</v>
@@ -2401,10 +2401,10 @@
         <v>0.380858</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.390437</v>
+        <v>0.267688</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.985029</v>
+        <v>0.877713</v>
       </c>
     </row>
     <row r="49">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -25923,7 +25923,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -28522,7 +28522,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -30624,7 +30624,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -32146,7 +32146,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -33386,7 +33386,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E393" s="5" t="n">

--- a/output/pdf_financials_xlsx/OCG.xlsx
+++ b/output/pdf_financials_xlsx/OCG.xlsx
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.217987</v>
+        <v>0.254905</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.216996</v>
+        <v>0.257244</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.32148</v>
+        <v>0.363696</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.328996</v>
+        <v>0.5524790000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.367574</v>
+        <v>0.424773</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.385215</v>
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.294244</v>
+        <v>0.331162</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.272677</v>
+        <v>0.312925</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.346065</v>
+        <v>0.388281</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.355047</v>
+        <v>0.57853</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.757503</v>
+        <v>0.814702</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>4.444315</v>
@@ -809,19 +809,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.294244</v>
+        <v>-0.331162</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.272677</v>
+        <v>-0.312925</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.346065</v>
+        <v>-0.388281</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.355047</v>
+        <v>-0.57853</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.757503</v>
+        <v>-0.814702</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-4.444315</v>
@@ -5215,16 +5215,16 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.03169</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.142238</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.000495</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -21797,7 +21797,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E226" s="5" t="n">
         <v>0.03169</v>
       </c>
@@ -29798,7 +29802,11 @@
           <t>Directors’ fees 13</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E341" s="5" t="n">
         <v>0.036918</v>
       </c>
